--- a/data/trans_orig/P6901-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6901-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>31782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>42291</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47818</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59989</t>
+          <t>59759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90788</t>
+          <t>91225</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113233</t>
+          <t>112073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50049</t>
+          <t>50524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66153</t>
+          <t>66644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>147894</t>
+          <t>148204</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174648</t>
+          <t>174363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46918</t>
+          <t>47203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73672</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76083</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96509</t>
+          <t>95807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47282</t>
+          <t>47968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61266</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127945</t>
+          <t>129224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154028</t>
+          <t>152834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>30221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49945</t>
+          <t>50520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>43236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68125</t>
+          <t>66846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74796</t>
+          <t>75021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92992</t>
+          <t>93895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34863</t>
+          <t>34163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103939</t>
+          <t>105505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125400</t>
+          <t>125359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36314</t>
+          <t>36089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>42642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35620</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>44923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>821</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,97 +2904,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>334550</t>
+          <t>335509</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>372165</t>
+          <t>372213</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>158216</t>
+          <t>158264</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>182869</t>
+          <t>183829</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>501482</t>
+          <t>501537</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>549421</t>
+          <t>546815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>100140</t>
+          <t>100092</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137755</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>36292</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61857</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>143006</t>
+          <t>145612</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>190945</t>
+          <t>190890</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>18613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57621</t>
+          <t>58096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73076</t>
+          <t>73550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43536</t>
+          <t>44004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57926</t>
+          <t>58021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106322</t>
+          <t>106715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127444</t>
+          <t>127610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46036</t>
+          <t>45643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56709</t>
+          <t>58125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76375</t>
+          <t>77302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49518</t>
+          <t>49284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>63432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113177</t>
+          <t>113721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135560</t>
+          <t>137298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41167</t>
+          <t>39751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34947</t>
+          <t>33209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57330</t>
+          <t>56786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59162</t>
+          <t>59937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76269</t>
+          <t>76425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84023</t>
+          <t>85028</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105754</t>
+          <t>106852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>30229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24733</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46464</t>
+          <t>45459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25777</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36886</t>
+          <t>37003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>18374</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>47923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59780</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>226963</t>
+          <t>227282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>260196</t>
+          <t>259495</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153383</t>
+          <t>153048</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178952</t>
+          <t>177544</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>389548</t>
+          <t>388400</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>431185</t>
+          <t>429377</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>67358</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>100591</t>
+          <t>100272</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60278</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>110029</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>151666</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>58374</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>73032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36977</t>
+          <t>37806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45347</t>
+          <t>45346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99909</t>
+          <t>99731</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116280</t>
+          <t>116437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27954</t>
+          <t>28132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78236</t>
+          <t>78949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96505</t>
+          <t>96149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>64670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135132</t>
+          <t>135684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158341</t>
+          <t>156888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34887</t>
+          <t>34174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49449</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49226</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68406</t>
+          <t>69429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50141</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92943</t>
+          <t>92476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117563</t>
+          <t>116433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42202</t>
+          <t>40191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29972</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>28905</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40508</t>
+          <t>40357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>53418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68121</t>
+          <t>67811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>242826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>277615</t>
+          <t>274945</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>171011</t>
+          <t>172284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192299</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>423295</t>
+          <t>422810</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>464402</t>
+          <t>463700</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72386</t>
+          <t>75056</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>107175</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45287</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>101897</t>
+          <t>102599</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>143004</t>
+          <t>143489</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>39195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54536</t>
+          <t>54409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25001</t>
+          <t>25661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38797</t>
+          <t>38669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69086</t>
+          <t>68516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90595</t>
+          <t>90289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>24288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>18733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39936</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64184</t>
+          <t>64679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81562</t>
+          <t>81424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53163</t>
+          <t>53779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65317</t>
+          <t>64940</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121749</t>
+          <t>121773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143820</t>
+          <t>141724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31347</t>
+          <t>30852</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22389</t>
+          <t>21773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49335</t>
+          <t>49311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60570</t>
+          <t>60883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81193</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110871</t>
+          <t>111323</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141036</t>
+          <t>140674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178025</t>
+          <t>178573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219953</t>
+          <t>221680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27360</t>
+          <t>27253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47983</t>
+          <t>47670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>43626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43549</t>
+          <t>41822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85477</t>
+          <t>84929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37675</t>
+          <t>37836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52176</t>
+          <t>52873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40775</t>
+          <t>40406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49341</t>
+          <t>49245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82250</t>
+          <t>82253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99178</t>
+          <t>98820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>29600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40693</t>
+          <t>40690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>229201</t>
+          <t>229067</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>264426</t>
+          <t>262543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>256445</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>297888</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>498342</t>
+          <t>497433</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>553674</t>
+          <t>552447</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75079</t>
+          <t>76962</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110304</t>
+          <t>110438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>56551</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>97770</t>
+          <t>97286</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140046</t>
+          <t>141273</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195378</t>
+          <t>196287</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
